--- a/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éléonore marche avec papa. Ils vont au marché. Éléonore tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Éléonore s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Éléonore sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Éléonore pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Éléonore marche avec papa. Ils vont au marché. Éléonore tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Éléonore s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Éléonore sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Éléonore pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Éléonore marche avec papa. Ils vont au marché. Éléonore tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Éléonore s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Éléonore sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
+papa|On s'arrête. Pieds au bord. Sur le trottoir.
+narrateur|Éléonore pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Éléonore arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Éléonore s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Éléonore donne la main à papa. Ils attendent un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Éléonore pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Éléonore arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Éléonore s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Éléonore donne la main à papa. Ils attendent un moment.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Éléonore s'arrête au trottoir</t>
+          <t>Le panier rouge de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les caisses du marché claquent au loin. Victorina et papa prennent le panier rouge. Au bord, Victorina s'arrête. Pieds au bord, sur le trottoir. La tomate est ronde.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éléonore marche avec papa. Ils vont au marché. Éléonore tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Éléonore s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Éléonore sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Éléonore pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Les caisses du marché claquent au loin. Clac, clac, tout doux. Le soleil tape sur les tuiles. Les tuiles sont chaudes, presque rouges. Une tomate roule un peu sur la table. Elle est ronde, un peu luisante. Le panier rouge attend près de la porte. L'anse est lisse, un peu usée. Victorina vit ici, avec papa. Papa, la tomate roule ! Oui. On va en chercher d'autres. Tu mets tes sandales ? En ce moment, Victorina s'assoit. Elle enfile la sandale gauche. Puis la sandale droite. La boucle fait un petit clic. Tu as fini tes sandales ? Oui, papa. Bravo. On prend le panier rouge. Papa ouvre la porte. L'air sent la tomate et le soleil. Ça sent le marché ! Oui. On marche sur le trottoir. Victorina donne la main à papa. Le panier tape un rythme léger. Les caisses claquent encore, plus près. Le soleil chauffe les cheveux. J'entends les caisses ! Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Victorina s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le panier rouge reste contre la jambe. Victorina serre la main de papa. Bravo, Victorina. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Éléonore marche avec papa. Ils vont au marché. Éléonore tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Éléonore s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Éléonore sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
-papa|On s'arrête. Pieds au bord. Sur le trottoir.
-narrateur|Éléonore pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>narrateur|Les caisses du marché claquent au loin.
+narrateur|Clac, clac, tout doux.
+narrateur|Le soleil tape sur les tuiles.
+narrateur|Les tuiles sont chaudes, presque rouges.
+narrateur|Une tomate roule un peu sur la table.
+narrateur|Elle est ronde, un peu luisante.
+narrateur|Le panier rouge attend près de la porte.
+narrateur|L'anse est lisse, un peu usée.
+narrateur|Victorina vit ici, avec papa.
+enfant-f|Papa, la tomate roule !
+papa|Oui.
+papa|On va en chercher d'autres.
+papa|Tu mets tes sandales ?
+narrateur|En ce moment, Victorina s'assoit.
+narrateur|Elle enfile la sandale gauche.
+narrateur|Puis la sandale droite.
+narrateur|La boucle fait un petit clic.
+papa|Tu as fini tes sandales ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|On prend le panier rouge.
+narrateur|Papa ouvre la porte.
+narrateur|L'air sent la tomate et le soleil.
+enfant-f|Ça sent le marché !
+papa|Oui.
+papa|On marche sur le trottoir.
+narrateur|Victorina donne la main à papa.
+narrateur|Le panier tape un rythme léger.
+narrateur|Les caisses claquent encore, plus près.
+narrateur|Le soleil chauffe les cheveux.
+enfant-f|J'entends les caisses !
+papa|Bientôt.
+papa|On reste sur le trottoir.
+narrateur|Le bord du trottoir arrive.
+narrateur|Le bord est gris et net.
+papa|On va s'arrêter.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+narrateur|Victorina s'arrête.
+narrateur|Ses pieds sont au bord.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+enfant-f|Je m'arrête.
+papa|Oui.
+papa|On attend avec papa.
+papa|Tes pieds sont calmes ?
+enfant-f|Oui.
+narrateur|Le panier rouge reste contre la jambe.
+narrateur|Victorina serre la main de papa.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Éléonore arrive au bord. Que fait-elle ?</t>
+          <t>Victorina arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1563,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Éléonore arrive au bord. Que fait-elle ?</t>
+          <t>narrateur|Victorina arrive au bord.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Éléonore s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>Victorina s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Victorina. On attend avec papa. La main de papa est chaude. L'anse du panier est lisse. Les caisses claquent encore, loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1740,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Éléonore s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>narrateur|Victorina s'arrête au bord.
+narrateur|Les pieds sont sur le trottoir.
+narrateur|Les pieds restent au bord.
+papa|Tu t'arrêtes au trottoir ?
+enfant-f|Oui.
+enfant-f|Je m'arrête.
+papa|Bravo, Victorina.
+papa|On attend avec papa.
+narrateur|La main de papa est chaude.
+narrateur|L'anse du panier est lisse.
+narrateur|Les caisses claquent encore, loin.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Éléonore donne la main à papa. Ils attendent un moment.</t>
+          <t>On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. Le marché sent la tomate mûre. Une caisse rouge est pleine. Tu poses une tomate ? Victorina la pose dans le panier. Elle est ronde ! Oui. Tu as fini de la poser ? Oui. Bravo. Le panier devient un peu lourd. Le soleil reste sur les tuiles.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1850,7 +1922,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Éléonore donne la main à papa. Ils attendent un moment.</t>
+          <t>papa|On y va ensemble ?
+enfant-f|Oui, papa.
+narrateur|Ils marchent avec l'adulte.
+narrateur|Le marché sent la tomate mûre.
+narrateur|Une caisse rouge est pleine.
+papa|Tu poses une tomate ?
+narrateur|Victorina la pose dans le panier.
+enfant-f|Elle est ronde !
+papa|Oui.
+papa|Tu as fini de la poser ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|Le panier devient un peu lourd.
+narrateur|Le soleil reste sur les tuiles.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1878,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Victorina. La tomate roule un peu dans le panier. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,7 +2103,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je me suis arrêtée.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+papa|Bravo, Victorina.
+narrateur|La tomate roule un peu dans le panier.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2040,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les caisses du marché claquent au loin. Clac, clac, tout doux. Le soleil tape sur les tuiles. Les tuiles sont chaudes, presque rouges. Une tomate roule un peu sur la table. Elle est ronde, un peu luisante. Le panier rouge attend près de la porte. L'anse est lisse, un peu usée. Victorina vit ici, avec papa. Papa, la tomate roule ! Oui. On va en chercher d'autres. Tu mets tes sandales ? En ce moment, Victorina s'assoit. Elle enfile la sandale gauche. Puis la sandale droite. La boucle fait un petit clic. Tu as fini tes sandales ? Oui, papa. Bravo. On prend le panier rouge. Papa ouvre la porte. L'air sent la tomate et le soleil. Ça sent le marché ! Oui. On marche sur le trottoir. Victorina donne la main à papa. Le panier tape un rythme léger. Les caisses claquent encore, plus près. Le soleil chauffe les cheveux. J'entends les caisses ! Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Victorina s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le panier rouge reste contre la jambe. Victorina serre la main de papa. Bravo, Victorina. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
+          <t>Les caisses du marché claquent au loin. Clac, clac, tout doux. Le soleil tape sur les tuiles. Les tuiles sont chaudes, presque rouges. Une tomate roule un peu sur la table. Elle est ronde, un peu luisante. Le panier rouge attend près de la porte. L'anse est lisse, un peu usée. Victorina vit ici, avec papa. Papa, la tomate roule ! Oui. On va en chercher d'autres. Tu mets tes sandales ? En ce moment, Victorina s'assoit. Elle enfile la sandale gauche. Puis la sandale droite. La boucle fait un petit clic. Tu as fini tes sandales ? Oui, papa. Bravo. On prend le panier rouge. Papa ouvre la porte. L'air sent la tomate et le soleil. Ça sent le marché ! Oui. On marche sur le trottoir. Victorina donne la main à papa. Le panier tape un rythme léger. Les caisses claquent encore, plus près. Le soleil chauffe les cheveux. J'entends les caisses ! Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Victorina s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le panier rouge reste contre la jambe. Victorina serre la main de papa. Bravo, Victorina. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Éléonore marche avec papa. Ils vont au marché. Éléonore tient la main de papa. Ils arrivent au bord. Le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt; est là. Papa s'arrête. Éléonore s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Éléonore sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Éléonore pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les caisses du marché claquent au loin. Clac, clac, tout doux. Le soleil tape sur les tuiles. Les tuiles sont chaudes, presque rouges. Une tomate roule un peu sur la table. Elle est ronde, un peu luisante. Le panier rouge attend près de la porte. L'anse est lisse, un peu usée. Victorina vit ici, avec papa. Papa, la tomate roule ! Oui. On va en chercher d'autres. Tu mets tes sandales ? En ce moment, Victorina s'assoit. Elle enfile la sandale gauche. Puis la sandale droite. La boucle fait un petit clic. Tu as fini tes sandales ? Oui, papa. Bravo. On prend le panier rouge. Papa ouvre la porte. L'air sent la tomate et le soleil. Ça sent le marché ! Oui. On marche sur le trottoir. Victorina donne la main à papa. Le panier tape un rythme léger. Les caisses claquent encore, plus près. Le soleil chauffe les cheveux. J'entends les caisses ! Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Victorina s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le panier rouge reste contre la jambe. Victorina serre la main de papa. Bravo, Victorina. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1374,11 +1374,9 @@
 narrateur|Le panier rouge reste contre la jambe.
 narrateur|Victorina serre la main de papa.
 papa|Bravo, Victorina.
-papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1408,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Éléonore arrive au bord. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1567,7 +1565,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1597,7 +1594,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Éléonore s'arrête au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Victorina. On attend avec papa. La main de papa est chaude. L'anse du panier est lisse. Les caisses claquent encore, loin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1753,7 +1750,6 @@
 narrateur|Les caisses claquent encore, loin.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Éléonore donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. Ils attendent un moment.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. Le marché sent la tomate mûre. Une caisse rouge est pleine. Tu poses une tomate ? Victorina la pose dans le panier. Elle est ronde ! Oui. Tu as fini de la poser ? Oui. Bravo. Le panier devient un peu lourd. Le soleil reste sur les tuiles.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1938,7 +1934,6 @@
 narrateur|Le soleil reste sur les tuiles.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Victorina. La tomate roule un peu dans le panier. L'histoire est finie.</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Victorina. La tomate roule un peu dans le panier.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Victorina. La tomate roule un peu dans le panier.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,11 +2102,9 @@
 papa|Pieds au bord.
 papa|Sur le trottoir.
 papa|Bravo, Victorina.
-narrateur|La tomate roule un peu dans le panier.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La tomate roule un peu dans le panier.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers le marché</t>
+          <t>maison ensoleillée, trottoir vers le marché</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Éléonore, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>
